--- a/02-VALUATION/M05/bus311-valuation-m05-l01-starter.xlsx
+++ b/02-VALUATION/M05/bus311-valuation-m05-l01-starter.xlsx
@@ -2,11 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Re9d97b33def14426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Timeline-Diagnose" sheetId="2" r:id="Rb8808e5d68fc40de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Build-Compare" sheetId="3" r:id="R57d96af1a23b4672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Sensitivity" sheetId="4" r:id="Rf15f9a6c36874829"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Checks-Decision" sheetId="5" r:id="R8dcebfe725884b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R63f62bda03394f36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Timeline-Diagnose" sheetId="2" r:id="R4bfb146812fb406a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Build-Compare" sheetId="3" r:id="R21e515c0db844fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Sensitivity" sheetId="4" r:id="R015a94c41f394a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Checks-Decision" sheetId="5" r:id="R417311a57ece4879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Rate-Applications" sheetId="6" r:id="Rf213a1999aae4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Preferred-Stock" sheetId="7" r:id="R35497a5d750149ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,12 +19,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
     <x:numFmt numFmtId="201" formatCode="0.00%;[Red](0.00%);-"/>
     <x:numFmt numFmtId="202" formatCode="#,##0;[Red](#,##0);-"/>
     <x:numFmt numFmtId="203" formatCode="@"/>
     <x:numFmt numFmtId="204" formatCode="0.00"/>
+    <x:numFmt numFmtId="205" formatCode="0.000"/>
   </x:numFmts>
   <x:fonts count="15">
     <x:font>
@@ -418,7 +421,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="243">
+  <x:cellXfs count="265">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1143,6 +1146,72 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="10" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1380,7 +1449,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="8" t="str">
-        <x:v>BUS311 · Valuation M05 · Student starter · Version 2026-07-28</x:v>
+        <x:v>BUS311 · Valuation M05 · Student starter · Version 2026-09-27</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -1402,7 +1471,7 @@
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
       <x:c r="A5" s="23" t="str">
-        <x:v>Decision objective: compare a cash purchase with beginning-of-month financing on the same valuation date. Complete the timeline before selecting functions, then normalize rates and periods, value both alternatives, stress-test the result, and state the choice in today’s dollars.</x:v>
+        <x:v>Compare a cash purchase with beginning-of-month financing on the same valuation date. Then use the same terms to solve for an implied financing rate, test a reserve horizon and real return, and value a separate hypothetical preferred share.</x:v>
       </x:c>
       <x:c r="B5" s="24"/>
       <x:c r="C5" s="24"/>
@@ -1477,7 +1546,7 @@
         <x:v>Normalize</x:v>
       </x:c>
       <x:c r="B11" s="42" t="str">
-        <x:v>Convert the quoted nominal APR to a periodic rate and calculate the EAR.</x:v>
+        <x:v>Convert the annual valuation discount rate to a monthly rate and calculate the EAR.</x:v>
       </x:c>
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="2"/>
@@ -1491,7 +1560,7 @@
         <x:v>Model</x:v>
       </x:c>
       <x:c r="B12" s="42" t="str">
-        <x:v>Use Excel PV and FV functions with linked cells; do not hard-code formula arguments.</x:v>
+        <x:v>Use linked PV and FV inputs; then use RATE and NPER on the rate-applications sheet.</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
       <x:c r="D12" s="2"/>
@@ -1583,7 +1652,7 @@
         <x:v>Model</x:v>
       </x:c>
       <x:c r="B19" s="42" t="str">
-        <x:v>Use real cell references for the rate, nper, pmt, pv/fv, and type arguments.</x:v>
+        <x:v>Use linked PV, FV, RATE, and NPER inputs; value the preferred dividend separately.</x:v>
       </x:c>
       <x:c r="C19" s="2"/>
       <x:c r="D19" s="2"/>
@@ -1734,7 +1803,7 @@
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="84" t="str">
-        <x:v>This is a clearly labeled Berkshire Hathaway teaching scenario; the cash amounts and financing quote are instructional assumptions, not company disclosures or an offer. If your instructor substitutes a FactSet-backed rate, record the field name, company, fiscal period, units, currency, retrieval date, and rate definition before using it.</x:v>
+        <x:v>This Berkshire Hathaway equipment scenario is hypothetical. The 9.6% annual rate is a valuation discount-rate assumption, not the financing offer’s stated APR. The cash amounts and preferred-share terms are teaching inputs, not company disclosures. Document the definition, units, period and source before replacing any rate.</x:v>
       </x:c>
       <x:c r="B30" s="85"/>
       <x:c r="C30" s="85"/>
@@ -1875,7 +1944,7 @@
       <x:c r="C6" s="31"/>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="31" t="str">
-        <x:v>Normalize the quote and choose functions</x:v>
+        <x:v>Normalize the valuation rate and choose functions</x:v>
       </x:c>
       <x:c r="F6" s="31"/>
       <x:c r="G6" s="31"/>
@@ -1929,13 +1998,13 @@
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="2" t="str">
-        <x:v>Quoted nominal APR</x:v>
+        <x:v>Annual valuation discount rate</x:v>
       </x:c>
       <x:c r="B9" s="105" t="n">
         <x:v>0.096</x:v>
       </x:c>
       <x:c r="C9" s="2" t="str">
-        <x:v>Compounded monthly</x:v>
+        <x:v>Nominal annual; compounded monthly</x:v>
       </x:c>
       <x:c r="D9" s="2"/>
       <x:c r="E9" s="2" t="str">
@@ -2893,7 +2962,7 @@
     </x:row>
     <x:row r="3" ht="29" customHeight="1">
       <x:c r="A3" s="84" t="str">
-        <x:v>Write one linked formula in B8 using the APR header in row 7 and monthly-payment input in column A. Lock only the rows/columns that should stay fixed, then copy the formula across and down. Every cell must recalculate the full payment-stream PV plus balloon PV.</x:v>
+        <x:v>Write one linked formula in B8 using the annual discount-rate header in row 7 and monthly-payment input in column A. Lock only the rows/columns that should stay fixed, then copy the formula across and down. Every cell must recalculate the payment-stream PV plus balloon PV.</x:v>
       </x:c>
       <x:c r="B3" s="85"/>
       <x:c r="C3" s="85"/>
@@ -2933,7 +3002,7 @@
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
       <x:c r="A7" s="99" t="str">
-        <x:v>Monthly payment  Nominal APR</x:v>
+        <x:v>Monthly payment  Annual discount rate</x:v>
       </x:c>
       <x:c r="B7" s="216" t="n">
         <x:v>0.06</x:v>
@@ -3007,7 +3076,7 @@
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
       <x:c r="A13" s="164" t="str">
-        <x:v>Copy audit: the base case is the intersection of −$3,150 per month and 9.60% APR. It must tie to the financing present cost on the model sheet.</x:v>
+        <x:v>Copy audit: the base case uses −$3,150 per month and a 9.60% annual discount rate. It must tie to the financing present cost on the model sheet.</x:v>
       </x:c>
       <x:c r="B13" s="165"/>
       <x:c r="C13" s="165"/>
@@ -3051,7 +3120,7 @@
     </x:row>
     <x:row r="17" ht="31" customHeight="1">
       <x:c r="A17" s="167" t="str">
-        <x:v>Across a row, what happens to PV cost as APR rises? Why?</x:v>
+        <x:v>Across a row, what happens to PV cost as the discount rate rises? Why?</x:v>
       </x:c>
       <x:c r="B17" s="144"/>
       <x:c r="C17" s="145"/>
@@ -3423,10 +3492,10 @@
         <x:v>Sensitivity rate direction</x:v>
       </x:c>
       <x:c r="B14" s="238" t="str">
-        <x:f>IF(COUNT('3 Sensitivity'!B8:F11)&lt;20,"",IF(AND('3 Sensitivity'!B9&gt;'3 Sensitivity'!C9,'3 Sensitivity'!C9&gt;'3 Sensitivity'!D9,'3 Sensitivity'!D9&gt;'3 Sensitivity'!E9,'3 Sensitivity'!E9&gt;'3 Sensitivity'!F9),"PV cost decreases as APR rises","CHECK"))</x:f>
+        <x:f>IF(COUNT('3 Sensitivity'!B8:F11)&lt;20,"",IF(AND('3 Sensitivity'!B9&gt;'3 Sensitivity'!C9,'3 Sensitivity'!C9&gt;'3 Sensitivity'!D9,'3 Sensitivity'!D9&gt;'3 Sensitivity'!E9,'3 Sensitivity'!E9&gt;'3 Sensitivity'!F9),"PV cost falls as discount rate rises","CHECK"))</x:f>
       </x:c>
       <x:c r="C14" s="61" t="str">
-        <x:v>PV cost decreases as APR rises</x:v>
+        <x:v>PV cost falls as discount rate rises</x:v>
       </x:c>
       <x:c r="D14" s="239"/>
       <x:c r="E14" s="240" t="str">
@@ -3437,7 +3506,7 @@
         <x:v>3 Sensitivity row 9</x:v>
       </x:c>
       <x:c r="G14" s="61" t="str">
-        <x:v>The direction check catches bad anchors and units.</x:v>
+        <x:v>Fixed future payments have a lower PV at a higher discount rate.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3631,4 +3700,918 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="65" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Solve the rate and time, then adjust for inflation</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+      <x:c r="H1" s="5"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3" ht="27" customHeight="1">
+      <x:c r="A3" s="84" t="str">
+        <x:v>The equipment terms are hypothetical. Treat 9.6% as the company’s annual valuation discount rate, compounded monthly. RATE finds the financing offer’s implied APR; NPER finds the time to a reserve target. Use effective annual rates with annual inflation.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+      <x:c r="G3" s="85"/>
+      <x:c r="H3" s="86"/>
+    </x:row>
+    <x:row r="4" ht="27" customHeight="1">
+      <x:c r="A4" s="90"/>
+      <x:c r="B4" s="91"/>
+      <x:c r="C4" s="91"/>
+      <x:c r="D4" s="91"/>
+      <x:c r="E4" s="91"/>
+      <x:c r="F4" s="91"/>
+      <x:c r="G4" s="91"/>
+      <x:c r="H4" s="92"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="2"/>
+      <x:c r="B5" s="2"/>
+      <x:c r="C5" s="2"/>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
+      <x:c r="A6" s="31" t="str">
+        <x:v>Implied rate of the equipment financing offer</x:v>
+      </x:c>
+      <x:c r="B6" s="31"/>
+      <x:c r="C6" s="31"/>
+      <x:c r="D6" s="31"/>
+      <x:c r="E6" s="31"/>
+      <x:c r="F6" s="31"/>
+      <x:c r="G6" s="31"/>
+      <x:c r="H6" s="31"/>
+    </x:row>
+    <x:row r="7" ht="29" customHeight="1">
+      <x:c r="A7" s="99" t="str">
+        <x:v>Offer input or result</x:v>
+      </x:c>
+      <x:c r="B7" s="100" t="str">
+        <x:v>Student cell</x:v>
+      </x:c>
+      <x:c r="C7" s="101" t="str">
+        <x:v>Unit and meaning</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+    </x:row>
+    <x:row r="8" ht="29" customHeight="1">
+      <x:c r="A8" s="2" t="str">
+        <x:v>Amount financed today</x:v>
+      </x:c>
+      <x:c r="B8" s="247" t="n">
+        <x:f>-'1 Timeline-Diagnose'!B8</x:f>
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="str">
+        <x:v>Positive company cash received at t = 0</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+    </x:row>
+    <x:row r="9" ht="29" customHeight="1">
+      <x:c r="A9" s="2" t="str">
+        <x:v>Beginning-of-month payment</x:v>
+      </x:c>
+      <x:c r="B9" s="248" t="n">
+        <x:f>'1 Timeline-Diagnose'!B12</x:f>
+        <x:v>-3150</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>Negative company cash flow each month</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+    </x:row>
+    <x:row r="10" ht="29" customHeight="1">
+      <x:c r="A10" s="2" t="str">
+        <x:v>Month 24 balloon</x:v>
+      </x:c>
+      <x:c r="B10" s="248" t="n">
+        <x:f>'1 Timeline-Diagnose'!B13</x:f>
+        <x:v>-8000</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="str">
+        <x:v>Negative company cash flow at the end</x:v>
+      </x:c>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+    </x:row>
+    <x:row r="11" ht="29" customHeight="1">
+      <x:c r="A11" s="2" t="str">
+        <x:v>Number of payments</x:v>
+      </x:c>
+      <x:c r="B11" s="249" t="n">
+        <x:f>'1 Timeline-Diagnose'!B11</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>Monthly intervals</x:v>
+      </x:c>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12" ht="29" customHeight="1">
+      <x:c r="A12" s="2" t="str">
+        <x:v>Payment type</x:v>
+      </x:c>
+      <x:c r="B12" s="250" t="n">
+        <x:f>'1 Timeline-Diagnose'!B14</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="str">
+        <x:v>1 = beginning of month</x:v>
+      </x:c>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+    </x:row>
+    <x:row r="13" ht="29" customHeight="1">
+      <x:c r="A13" s="2" t="str">
+        <x:v>Implied monthly rate</x:v>
+      </x:c>
+      <x:c r="B13" s="254"/>
+      <x:c r="C13" s="2" t="str">
+        <x:v>RATE output per month</x:v>
+      </x:c>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14" ht="29" customHeight="1">
+      <x:c r="A14" s="2" t="str">
+        <x:v>Implied nominal APR</x:v>
+      </x:c>
+      <x:c r="B14" s="255"/>
+      <x:c r="C14" s="2" t="str">
+        <x:v>Monthly rate multiplied by 12</x:v>
+      </x:c>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15" ht="29" customHeight="1">
+      <x:c r="A15" s="2" t="str">
+        <x:v>Implied effective annual rate</x:v>
+      </x:c>
+      <x:c r="B15" s="255"/>
+      <x:c r="C15" s="2" t="str">
+        <x:v>Compounded financing cost</x:v>
+      </x:c>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16" ht="29" customHeight="1">
+      <x:c r="A16" s="2" t="str">
+        <x:v>Implied APR minus valuation rate</x:v>
+      </x:c>
+      <x:c r="B16" s="256"/>
+      <x:c r="C16" s="2" t="str">
+        <x:v>Percentage-point difference</x:v>
+      </x:c>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="31" t="str">
+        <x:v>Replacement reserve horizon</x:v>
+      </x:c>
+      <x:c r="B18" s="31"/>
+      <x:c r="C18" s="31"/>
+      <x:c r="D18" s="31"/>
+      <x:c r="E18" s="31"/>
+      <x:c r="F18" s="31"/>
+      <x:c r="G18" s="31"/>
+      <x:c r="H18" s="31"/>
+    </x:row>
+    <x:row r="19" ht="30" customHeight="1">
+      <x:c r="A19" s="99" t="str">
+        <x:v>Reserve input or result</x:v>
+      </x:c>
+      <x:c r="B19" s="100" t="str">
+        <x:v>Student cell</x:v>
+      </x:c>
+      <x:c r="C19" s="101" t="str">
+        <x:v>Unit and meaning</x:v>
+      </x:c>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="2" t="str">
+        <x:v>Amount invested today</x:v>
+      </x:c>
+      <x:c r="B20" s="257" t="n">
+        <x:f>-'1 Timeline-Diagnose'!B8</x:f>
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="C20" s="2" t="str">
+        <x:v>Positive balance; enter as an outflow in NPER</x:v>
+      </x:c>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="A21" s="2" t="str">
+        <x:v>Replacement target</x:v>
+      </x:c>
+      <x:c r="B21" s="104" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="str">
+        <x:v>Hypothetical equipment reserve target</x:v>
+      </x:c>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22" ht="30" customHeight="1">
+      <x:c r="A22" s="2" t="str">
+        <x:v>Monthly growth assumption</x:v>
+      </x:c>
+      <x:c r="B22" s="258" t="str">
+        <x:f>IF('1 Timeline-Diagnose'!F8="","",'1 Timeline-Diagnose'!F8)</x:f>
+      </x:c>
+      <x:c r="C22" s="2" t="str">
+        <x:v>Teaching assumption linked to the monthly model rate</x:v>
+      </x:c>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23" ht="30" customHeight="1">
+      <x:c r="A23" s="2" t="str">
+        <x:v>Months to reach target</x:v>
+      </x:c>
+      <x:c r="B23" s="260"/>
+      <x:c r="C23" s="2" t="str">
+        <x:v>NPER may return part of a month</x:v>
+      </x:c>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24" ht="30" customHeight="1">
+      <x:c r="A24" s="2" t="str">
+        <x:v>First whole month at target</x:v>
+      </x:c>
+      <x:c r="B24" s="117"/>
+      <x:c r="C24" s="2" t="str">
+        <x:v>Round up; then check the future balance</x:v>
+      </x:c>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
+      <x:c r="C26" s="2"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="31" t="str">
+        <x:v>Real annual return after inflation</x:v>
+      </x:c>
+      <x:c r="B27" s="31"/>
+      <x:c r="C27" s="31"/>
+      <x:c r="D27" s="31"/>
+      <x:c r="E27" s="31"/>
+      <x:c r="F27" s="31"/>
+      <x:c r="G27" s="31"/>
+      <x:c r="H27" s="31"/>
+    </x:row>
+    <x:row r="28" ht="30" customHeight="1">
+      <x:c r="A28" s="99" t="str">
+        <x:v>Annual input or result</x:v>
+      </x:c>
+      <x:c r="B28" s="100" t="str">
+        <x:v>Student cell</x:v>
+      </x:c>
+      <x:c r="C28" s="101" t="str">
+        <x:v>Unit and meaning</x:v>
+      </x:c>
+      <x:c r="D28" s="2"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="2"/>
+    </x:row>
+    <x:row r="29" ht="30" customHeight="1">
+      <x:c r="A29" s="2" t="str">
+        <x:v>Inflation assumption</x:v>
+      </x:c>
+      <x:c r="B29" s="105" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="C29" s="2" t="str">
+        <x:v>Hypothetical annual inflation rate</x:v>
+      </x:c>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30" ht="30" customHeight="1">
+      <x:c r="A30" s="2" t="str">
+        <x:v>Effective nominal annual rate</x:v>
+      </x:c>
+      <x:c r="B30" s="258" t="str">
+        <x:f>IF('1 Timeline-Diagnose'!F10="","",'1 Timeline-Diagnose'!F10)</x:f>
+      </x:c>
+      <x:c r="C30" s="2" t="str">
+        <x:v>Link to the annual effective valuation rate</x:v>
+      </x:c>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+    </x:row>
+    <x:row r="31" ht="30" customHeight="1">
+      <x:c r="A31" s="2" t="str">
+        <x:v>Exact real annual rate</x:v>
+      </x:c>
+      <x:c r="B31" s="254"/>
+      <x:c r="C31" s="2" t="str">
+        <x:v>Use annual rates in both numerator and denominator</x:v>
+      </x:c>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+    </x:row>
+    <x:row r="32" ht="30" customHeight="1">
+      <x:c r="A32" s="2" t="str">
+        <x:v>Nominal less inflation</x:v>
+      </x:c>
+      <x:c r="B32" s="255"/>
+      <x:c r="C32" s="2" t="str">
+        <x:v>Approximation for comparison</x:v>
+      </x:c>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+    <x:row r="33" ht="30" customHeight="1">
+      <x:c r="A33" s="2" t="str">
+        <x:v>Exact minus approximate</x:v>
+      </x:c>
+      <x:c r="B33" s="256"/>
+      <x:c r="C33" s="2" t="str">
+        <x:v>Percentage-point gap</x:v>
+      </x:c>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+    </x:row>
+    <x:row r="35" ht="29" customHeight="1">
+      <x:c r="A35" s="262" t="str">
+        <x:v>Audit: RATE is the financing offer’s implied rate. The 9.6% rate values fixed cash flows for the company. Changing a valuation discount rate while holding payments fixed does not describe a repriced loan quote.</x:v>
+      </x:c>
+      <x:c r="B35" s="262"/>
+      <x:c r="C35" s="262"/>
+      <x:c r="D35" s="262"/>
+      <x:c r="E35" s="262"/>
+      <x:c r="F35" s="262"/>
+      <x:c r="G35" s="262"/>
+      <x:c r="H35" s="262"/>
+    </x:row>
+    <x:row r="36" ht="29" customHeight="1">
+      <x:c r="A36" s="262"/>
+      <x:c r="B36" s="262"/>
+      <x:c r="C36" s="262"/>
+      <x:c r="D36" s="262"/>
+      <x:c r="E36" s="262"/>
+      <x:c r="F36" s="262"/>
+      <x:c r="G36" s="262"/>
+      <x:c r="H36" s="262"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H4"/>
+    <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A18:H18"/>
+    <x:mergeCell ref="A27:H27"/>
+    <x:mergeCell ref="A35:H36"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="67" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Value a level preferred dividend</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+      <x:c r="H1" s="5"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3" ht="27" customHeight="1">
+      <x:c r="A3" s="84" t="str">
+        <x:v>A Berkshire treasury team considers a hypothetical preferred share. The first level dividend arrives next quarter and payments continue indefinitely. These terms are teaching assumptions, not a real security quote.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+      <x:c r="G3" s="85"/>
+      <x:c r="H3" s="86"/>
+    </x:row>
+    <x:row r="4" ht="27" customHeight="1">
+      <x:c r="A4" s="90"/>
+      <x:c r="B4" s="91"/>
+      <x:c r="C4" s="91"/>
+      <x:c r="D4" s="91"/>
+      <x:c r="E4" s="91"/>
+      <x:c r="F4" s="91"/>
+      <x:c r="G4" s="91"/>
+      <x:c r="H4" s="92"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="2"/>
+      <x:c r="B5" s="2"/>
+      <x:c r="C5" s="2"/>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
+      <x:c r="A6" s="31" t="str">
+        <x:v>Quarterly dividend and required return</x:v>
+      </x:c>
+      <x:c r="B6" s="31"/>
+      <x:c r="C6" s="31"/>
+      <x:c r="D6" s="31"/>
+      <x:c r="E6" s="31"/>
+      <x:c r="F6" s="31"/>
+      <x:c r="G6" s="31"/>
+      <x:c r="H6" s="31"/>
+    </x:row>
+    <x:row r="7" ht="31" customHeight="1">
+      <x:c r="A7" s="99" t="str">
+        <x:v>Preferred-share input or result</x:v>
+      </x:c>
+      <x:c r="B7" s="100" t="str">
+        <x:v>Student cell</x:v>
+      </x:c>
+      <x:c r="C7" s="101" t="str">
+        <x:v>Unit and meaning</x:v>
+      </x:c>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+    </x:row>
+    <x:row r="8" ht="31" customHeight="1">
+      <x:c r="A8" s="2" t="str">
+        <x:v>Dividend each quarter</x:v>
+      </x:c>
+      <x:c r="B8" s="104" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="str">
+        <x:v>Cash paid per share next quarter and thereafter</x:v>
+      </x:c>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+    </x:row>
+    <x:row r="9" ht="31" customHeight="1">
+      <x:c r="A9" s="2" t="str">
+        <x:v>Nominal annual required return</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>Compounded quarterly</x:v>
+      </x:c>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+    </x:row>
+    <x:row r="10" ht="31" customHeight="1">
+      <x:c r="A10" s="2" t="str">
+        <x:v>Quarters per year</x:v>
+      </x:c>
+      <x:c r="B10" s="112" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="str">
+        <x:v>Match rate and dividend frequency</x:v>
+      </x:c>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+    </x:row>
+    <x:row r="11" ht="31" customHeight="1">
+      <x:c r="A11" s="2" t="str">
+        <x:v>First dividend</x:v>
+      </x:c>
+      <x:c r="B11" s="263" t="str">
+        <x:v>Next quarter</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>The level-perpetuity formula assumes one period from now</x:v>
+      </x:c>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12" ht="31" customHeight="1">
+      <x:c r="A12" s="2" t="str">
+        <x:v>Required return per quarter</x:v>
+      </x:c>
+      <x:c r="B12" s="115"/>
+      <x:c r="C12" s="2" t="str">
+        <x:v>Annual nominal rate divided by four</x:v>
+      </x:c>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+    </x:row>
+    <x:row r="13" ht="31" customHeight="1">
+      <x:c r="A13" s="2" t="str">
+        <x:v>Value per share today</x:v>
+      </x:c>
+      <x:c r="B13" s="192"/>
+      <x:c r="C13" s="2" t="str">
+        <x:v>Quarterly dividend divided by quarterly return</x:v>
+      </x:c>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14" ht="31" customHeight="1">
+      <x:c r="A14" s="2" t="str">
+        <x:v>Annual dividends per share</x:v>
+      </x:c>
+      <x:c r="B14" s="194"/>
+      <x:c r="C14" s="2" t="str">
+        <x:v>Four level dividends</x:v>
+      </x:c>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15" ht="31" customHeight="1">
+      <x:c r="A15" s="2" t="str">
+        <x:v>Annual dividend yield at calculated value</x:v>
+      </x:c>
+      <x:c r="B15" s="115"/>
+      <x:c r="C15" s="2" t="str">
+        <x:v>Reasonableness check</x:v>
+      </x:c>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2"/>
+      <x:c r="B16" s="2"/>
+      <x:c r="C16" s="2"/>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="31" t="str">
+        <x:v>Treasury investment size</x:v>
+      </x:c>
+      <x:c r="B17" s="31"/>
+      <x:c r="C17" s="31"/>
+      <x:c r="D17" s="31"/>
+      <x:c r="E17" s="31"/>
+      <x:c r="F17" s="31"/>
+      <x:c r="G17" s="31"/>
+      <x:c r="H17" s="31"/>
+    </x:row>
+    <x:row r="18" ht="31" customHeight="1">
+      <x:c r="A18" s="99" t="str">
+        <x:v>Investment input or result</x:v>
+      </x:c>
+      <x:c r="B18" s="100" t="str">
+        <x:v>Student cell</x:v>
+      </x:c>
+      <x:c r="C18" s="101" t="str">
+        <x:v>Unit and meaning</x:v>
+      </x:c>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="2"/>
+    </x:row>
+    <x:row r="19" ht="31" customHeight="1">
+      <x:c r="A19" s="2" t="str">
+        <x:v>Available investment budget</x:v>
+      </x:c>
+      <x:c r="B19" s="104" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="str">
+        <x:v>Hypothetical treasury allocation</x:v>
+      </x:c>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20" ht="31" customHeight="1">
+      <x:c r="A20" s="2" t="str">
+        <x:v>Whole shares affordable</x:v>
+      </x:c>
+      <x:c r="B20" s="117"/>
+      <x:c r="C20" s="2" t="str">
+        <x:v>Do not exceed the budget</x:v>
+      </x:c>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2"/>
+      <x:c r="B21" s="2"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="31" t="str">
+        <x:v>Check the perpetuity conditions</x:v>
+      </x:c>
+      <x:c r="B22" s="31"/>
+      <x:c r="C22" s="31"/>
+      <x:c r="D22" s="31"/>
+      <x:c r="E22" s="31"/>
+      <x:c r="F22" s="31"/>
+      <x:c r="G22" s="31"/>
+      <x:c r="H22" s="31"/>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="84" t="str">
+        <x:v>The shortcut requires level payments forever, a first payment one quarter from today, and a quarterly required return. The 24-payment equipment loan is finite and cannot use this shortcut.</x:v>
+      </x:c>
+      <x:c r="B23" s="85"/>
+      <x:c r="C23" s="85"/>
+      <x:c r="D23" s="85"/>
+      <x:c r="E23" s="85"/>
+      <x:c r="F23" s="85"/>
+      <x:c r="G23" s="85"/>
+      <x:c r="H23" s="86"/>
+    </x:row>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="90"/>
+      <x:c r="B24" s="91"/>
+      <x:c r="C24" s="91"/>
+      <x:c r="D24" s="91"/>
+      <x:c r="E24" s="91"/>
+      <x:c r="F24" s="91"/>
+      <x:c r="G24" s="91"/>
+      <x:c r="H24" s="92"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="264" t="str">
+        <x:v>Interpretation</x:v>
+      </x:c>
+      <x:c r="B26" s="144"/>
+      <x:c r="C26" s="145"/>
+      <x:c r="D26" s="145"/>
+      <x:c r="E26" s="145"/>
+      <x:c r="F26" s="145"/>
+      <x:c r="G26" s="145"/>
+      <x:c r="H26" s="146"/>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="A27" s="264"/>
+      <x:c r="B27" s="147"/>
+      <x:c r="C27" s="148"/>
+      <x:c r="D27" s="148"/>
+      <x:c r="E27" s="148"/>
+      <x:c r="F27" s="148"/>
+      <x:c r="G27" s="148"/>
+      <x:c r="H27" s="149"/>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="264"/>
+      <x:c r="B28" s="150"/>
+      <x:c r="C28" s="151"/>
+      <x:c r="D28" s="151"/>
+      <x:c r="E28" s="151"/>
+      <x:c r="F28" s="151"/>
+      <x:c r="G28" s="151"/>
+      <x:c r="H28" s="152"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H4"/>
+    <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A17:H17"/>
+    <x:mergeCell ref="A22:H22"/>
+    <x:mergeCell ref="A23:H24"/>
+    <x:mergeCell ref="A26:A28"/>
+    <x:mergeCell ref="B26:H28"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>